--- a/Result/profitability/2014.xlsx
+++ b/Result/profitability/2014.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.85</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.125</v>
+        <v>-0.05125000000000002</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.96375</v>
+        <v>-1.8575</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.48</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1125</v>
+        <v>0.14</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3000000000000003</v>
+        <v>0.4662500000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>0.24125</v>
+        <v>0.28125</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3225</v>
+        <v>2.49125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-6.24</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.52</v>
+        <v>-0.42625</v>
       </c>
       <c r="N5" t="n">
-        <v>-26.0075</v>
+        <v>-23.325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-2.23</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7262500000000001</v>
+        <v>-0.6587500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-29.3525</v>
+        <v>-27.22625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6537499999999999</v>
+        <v>-0.6100000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-26.9875</v>
+        <v>-25.76</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.07</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4975000000000001</v>
+        <v>-0.46375</v>
       </c>
       <c r="N8" t="n">
-        <v>-24.25</v>
+        <v>-23.3625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5808</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5451</v>
+      </c>
+      <c r="E75" t="n">
+        <v>357</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G75" t="n">
+        <v>254</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>248</v>
+      </c>
+      <c r="K75" t="n">
+        <v>248</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-4.815</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.100000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-7.473684210526317</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.293103448275862</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.401698236446767</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
